--- a/Produksi_Beras_2023_Analisis_Regresi.xlsx
+++ b/Produksi_Beras_2023_Analisis_Regresi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aa8cdabbe2ef22eb/Dokumen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{425A8F2B-1E81-4A36-A452-79135D106938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{425A8F2B-1E81-4A36-A452-79135D106938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45995A5F-1F37-45B0-9B53-73087C79ED84}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CAC037AC-6F4C-48A9-936E-83B98FD7BAEF}"/>
   </bookViews>
@@ -180,7 +180,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,6 +193,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -241,14 +251,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -258,8 +266,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -604,915 +619,915 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <v>1404234.82</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="5">
         <v>5683475</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="5">
         <v>254287.38</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="5">
         <v>55.22</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="5">
         <v>41408</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="5">
         <v>808955.47</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="4">
         <v>2087474.15</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="5">
         <v>7246074.0000000009</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="5">
         <v>406109.49</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="5">
         <v>51.4</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="5">
         <v>68306</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="5">
         <v>1197409.21</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="4">
         <v>1482468.79</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="5">
         <v>4211954</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="5">
         <v>300564.77</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="5">
         <v>49.32</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="5">
         <v>54327</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="5">
         <v>858383.18</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="4">
         <v>205972.55</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="5">
         <v>8993590</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="5">
         <v>51914.14</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="5">
         <v>39.68</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="5">
         <v>154522</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="5">
         <v>118208.51</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>275941.45</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="5">
         <v>4902658</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="5">
         <v>61236.639999999999</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="5">
         <v>45.06</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="5">
         <v>79850</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="5">
         <v>159624.9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="4">
         <v>2832773.92</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="5">
         <v>8677168</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="5">
         <v>504143.03</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="5">
         <v>56.19</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="5">
         <v>71958</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="5">
         <v>1626734.93</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="4">
         <v>286684.43</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="5">
         <v>2012834</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="5">
         <v>57877.18</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="5">
         <v>49.53</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="5">
         <v>46300</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="5">
         <v>165120.07999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="4">
         <v>2757898.19</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="5">
         <v>3357026</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="5">
         <v>530108.09</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="5">
         <v>52.03</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="5">
         <v>48191</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="5">
         <v>1585385.58</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="4">
         <v>66468.89</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="5">
         <v>1669013</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="5">
         <v>15284.56</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="5">
         <v>43.49</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="5">
         <v>67813</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="5">
         <v>39398.129999999997</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="4">
         <v>324.01</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="5">
         <v>826970.99999999988</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="5">
         <v>115.27</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="5">
         <v>28.11</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="5">
         <v>154065</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="5">
         <v>185.41</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="4">
         <v>2674.28</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="5">
         <v>66098</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="5">
         <v>542.92999999999995</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="5">
         <v>49.26</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="5">
         <v>322619</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="5">
         <v>1576.37</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="4">
         <v>9140039.1999999993</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="5">
         <v>3704486</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="5">
         <v>1583656.28</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="5">
         <v>57.71</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="5">
         <v>52652</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="5">
         <v>5278209.2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="4">
         <v>9084107.5299999993</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="5">
         <v>3433749</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="5">
         <v>1642761.23</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="5">
         <v>55.3</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="5">
         <v>45167</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="5">
         <v>5223899.08</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="4">
         <v>534113.68999999994</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="5">
         <v>317065</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="5">
         <v>105693.66</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="5">
         <v>50.53</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="5">
         <v>48360</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="5">
         <v>303390.05</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="4">
         <v>9710661.3300000001</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="5">
         <v>4803684</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="5">
         <v>1698083.31</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="5">
         <v>57.19</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="5">
         <v>71122</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="5">
         <v>5607131.5300000003</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="4">
         <v>1686483.29</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="5">
         <v>935277</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="5">
         <v>311199.73</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="5">
         <v>54.19</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="5">
         <v>66147</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="5">
         <v>960504.4</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="4">
         <v>673580.65</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="5">
         <v>559015</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="5">
         <v>108514.06</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="5">
         <v>62.07</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="5">
         <v>62294</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="5">
         <v>379869.53</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="4">
         <v>1538536.92</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="5">
         <v>1967589</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="5">
         <v>287512.14</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="5">
         <v>53.51</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="5">
         <v>29926</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="5">
         <v>876273.53</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="4">
         <v>766810.46</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="5">
         <v>4644664</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="5">
         <v>184698.89</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="5">
         <v>41.52</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="5">
         <v>23078</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="5">
         <v>449144.5</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="4">
         <v>700290.8</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="5">
         <v>14703704</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="5">
         <v>224068.52</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="5">
         <v>31.25</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="5">
         <v>48809</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="5">
         <v>414286.15</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="4">
         <v>330781.05</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="5">
         <v>15344391</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="5">
         <v>101580.3</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="5">
         <v>32.56</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="5">
         <v>75271</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="5">
         <v>196487.84</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="4">
         <v>875545.73</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="5">
         <v>3713505.0000000005</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="5">
         <v>214283.82</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="5">
         <v>40.86</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="5">
         <v>63754</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="5">
         <v>518040.84</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="4">
         <v>226972.07</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="5">
         <v>12698128</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="5">
         <v>57082.01</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="5">
         <v>39.76</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="5">
         <v>215761</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="5">
         <v>132022.44</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="4">
         <v>23602</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="5">
         <v>7010117.9999999991</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="5">
         <v>6499.92</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="5">
         <v>36.31</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="5">
         <v>201749</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="5">
         <v>13992.14</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="4">
         <v>238193.41</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="5">
         <v>1450028</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="5">
         <v>54562.95</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="5">
         <v>43.65</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="5">
         <v>64131</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="5">
         <v>133848.82</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="4">
         <v>821367.41</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="5">
         <v>6160572</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="5">
         <v>177699.03</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="5">
         <v>46.22</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="5">
         <v>112461</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="5">
         <v>484835.84000000003</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="4">
         <v>4876386.1100000003</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="5">
         <v>4533055</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="5">
         <v>967790.21</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="5">
         <v>50.39</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="5">
         <v>69710</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="5">
         <v>2798247.6</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="4">
         <v>479407.25</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="5">
         <v>3615971</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="5">
         <v>113930.26</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="5">
         <v>42.08</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="5">
         <v>64088</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="5">
         <v>275313.62</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="4">
         <v>251431.76</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="5">
         <v>1202515</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="5">
         <v>49610.47</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="5">
         <v>50.68</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="5">
         <v>42341</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="5">
         <v>140390</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="4">
         <v>291458.59000000003</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="5">
         <v>1659475</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="5">
         <v>58606.67</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="5">
         <v>49.73</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="5">
         <v>39547</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" s="5">
         <v>167391.99</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="4">
         <v>79958.34</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="5">
         <v>4615827</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="5">
         <v>22636.68</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="5">
         <v>35.32</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="5">
         <v>30455</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" s="5">
         <v>44777.38</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="4">
         <v>26663.23</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="5">
         <v>3299869.9999999995</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="5">
         <v>7709.07</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="5">
         <v>34.590000000000003</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="5">
         <v>63675</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" s="5">
         <v>14920.97</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="4">
         <v>22566.81</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="5">
         <v>6027531</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="5">
         <v>5006.2700000000004</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="5">
         <v>45.08</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="5">
         <v>108110</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="5">
         <v>13559.26</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="4">
         <v>2396.9499999999998</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="5">
         <v>3912294.9999999995</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="5">
         <v>579.83000000000004</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="5">
         <v>41.34</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="5">
         <v>58450</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" s="5">
         <v>1440.2</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="4">
         <v>3760.45</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="5">
         <v>8268096.0000000009</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="5">
         <v>840.18</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="5">
         <v>44.76</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="5">
         <v>78055</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" s="5">
         <v>2147.17</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="4">
         <v>183627.83</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="5">
         <v>11784916</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="5">
         <v>44807.86</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="5">
         <v>40.98</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="5">
         <v>58677</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" s="5">
         <v>104849.17</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="4">
         <v>9273.2199999999993</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="5">
         <v>6107291</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="5">
         <v>2094.1999999999998</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="5">
         <v>44.28</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="5">
         <v>103508</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="5">
         <v>5294.89</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="4">
         <v>61.63</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="5">
         <v>5121333</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="5">
         <v>14.14</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="5">
         <v>43.59</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="5">
         <v>16870</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G39" s="5">
         <v>35.19</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="4"/>
+      <c r="B41" s="3"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
